--- a/member_list.xlsx
+++ b/member_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philippaadolf/Documents/R/Website_sfb_redefi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD72252-D439-F44E-B035-5589512A960C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7247BC-5A5B-D048-A70F-4267A1037335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>Martina Barili</t>
   </si>
   <si>
-    <t>PhD student</t>
-  </si>
-  <si>
     <t>/img/pictures/Martina_Barili.jpeg</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
   </si>
   <si>
     <t>Sarah Melker</t>
-  </si>
-  <si>
-    <t>Postdoc researcher</t>
   </si>
   <si>
     <t>/img/pictures/Sarah_Melker.jpeg</t>
@@ -225,9 +219,6 @@
   </si>
   <si>
     <t>Caroline Gardner</t>
-  </si>
-  <si>
-    <t>Student assistant</t>
   </si>
   <si>
     <t>Univ.-Prof. PhD Boban Arsenijević</t>
@@ -700,6 +691,15 @@
   <si>
     <t>Daniel Büring received his PhD from the University of Tübingen and is Professor of Linguistics at the University of Vienna. His research in formal semantics and pragmatics covers intonation and meaning, binding theory, comparatives, discourse particles, and tense.</t>
   </si>
+  <si>
+    <t>PhD Student</t>
+  </si>
+  <si>
+    <t>Postdoc Researcher</t>
+  </si>
+  <si>
+    <t>Student Assistant</t>
+  </si>
 </sst>
 </file>
 
@@ -1132,24 +1132,24 @@
       <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
@@ -1163,23 +1163,23 @@
     </row>
     <row r="5" spans="1:28" ht="42">
       <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
+      <c r="D5" s="9" t="s">
+        <v>223</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>17</v>
@@ -1198,66 +1198,66 @@
     </row>
     <row r="6" spans="1:28" ht="42">
       <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="56">
       <c r="A7" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
+      <c r="D7" s="9" t="s">
+        <v>223</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8" spans="1:28" ht="42">
       <c r="A8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
@@ -1312,34 +1312,34 @@
     </row>
     <row r="9" spans="1:28" ht="70">
       <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
@@ -1354,28 +1354,28 @@
     </row>
     <row r="10" spans="1:28" ht="42">
       <c r="A10" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>224</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1392,16 +1392,16 @@
     </row>
     <row r="11" spans="1:28" ht="42">
       <c r="A11" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>225</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>14</v>
@@ -1409,7 +1409,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1426,34 +1426,34 @@
     </row>
     <row r="12" spans="1:28" ht="84">
       <c r="A12" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -1468,34 +1468,34 @@
     </row>
     <row r="13" spans="1:28" ht="70">
       <c r="A13" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>24</v>
+        <v>68</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>223</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
@@ -1510,34 +1510,34 @@
     </row>
     <row r="14" spans="1:28" ht="56">
       <c r="A14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -1552,34 +1552,34 @@
     </row>
     <row r="15" spans="1:28" ht="56">
       <c r="A15" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -1594,34 +1594,34 @@
     </row>
     <row r="16" spans="1:28" ht="70">
       <c r="A16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="J16" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
@@ -1636,34 +1636,34 @@
     </row>
     <row r="17" spans="1:28" ht="70">
       <c r="A17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
@@ -1678,34 +1678,34 @@
     </row>
     <row r="18" spans="1:28" ht="56">
       <c r="A18" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="J18" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
@@ -1719,34 +1719,34 @@
     </row>
     <row r="19" spans="1:28" ht="56">
       <c r="A19" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="H19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
@@ -1760,34 +1760,34 @@
     </row>
     <row r="20" spans="1:28" ht="42">
       <c r="A20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="H20" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="J20" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -1801,34 +1801,34 @@
     </row>
     <row r="21" spans="1:28" ht="84">
       <c r="A21" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
@@ -1842,34 +1842,34 @@
     </row>
     <row r="22" spans="1:28" ht="56">
       <c r="A22" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="H22" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>146</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
@@ -1883,34 +1883,34 @@
     </row>
     <row r="23" spans="1:28" ht="56">
       <c r="A23" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="H23" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="F23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
@@ -1924,34 +1924,34 @@
     </row>
     <row r="24" spans="1:28" ht="70">
       <c r="A24" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
@@ -1965,34 +1965,34 @@
     </row>
     <row r="25" spans="1:28" ht="69" customHeight="1">
       <c r="A25" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
@@ -2006,34 +2006,34 @@
     </row>
     <row r="26" spans="1:28" ht="56">
       <c r="A26" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
@@ -2047,28 +2047,28 @@
     </row>
     <row r="27" spans="1:28" ht="42">
       <c r="A27" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="H27" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -2084,34 +2084,34 @@
     </row>
     <row r="28" spans="1:28" ht="70">
       <c r="A28" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="H28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I28" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="J28" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -2125,34 +2125,34 @@
     </row>
     <row r="29" spans="1:28" ht="42">
       <c r="A29" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="H29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="J29" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
@@ -30032,114 +30032,114 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/member_list.xlsx
+++ b/member_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philippaadolf/Documents/R/Website_sfb_redefi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7247BC-5A5B-D048-A70F-4267A1037335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA93BAD-FA36-0B41-B135-CE343CE4911A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,9 +671,6 @@
     <t>https://uni-salzburg.elsevierpure.com/de/persons/anita-riedl/</t>
   </si>
   <si>
-    <t>/img/pictures/Daniel_Büring.jpg</t>
-  </si>
-  <si>
     <t>/img/pictures/Dalina_Kallulli.jpeg</t>
   </si>
   <si>
@@ -699,6 +696,9 @@
   </si>
   <si>
     <t>Student Assistant</t>
+  </si>
+  <si>
+    <t>/img/pictures/Daniel_Buering.jpg</t>
   </si>
 </sst>
 </file>
@@ -982,6 +982,7 @@
   <cols>
     <col min="1" max="1" width="38.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
     <col min="6" max="6" width="87.33203125" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="9" max="9" width="150" style="1" customWidth="1"/>
@@ -1133,7 +1134,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>24</v>
@@ -1172,10 +1173,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -1207,7 +1208,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>33</v>
@@ -1239,7 +1240,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>40</v>
@@ -1321,7 +1322,7 @@
         <v>47</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>55</v>
@@ -1363,7 +1364,7 @@
         <v>47</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>14</v>
@@ -1401,7 +1402,7 @@
         <v>47</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>14</v>
@@ -1477,7 +1478,7 @@
         <v>68</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>14</v>
@@ -1519,7 +1520,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>81</v>
@@ -1564,7 +1565,7 @@
         <v>21</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>89</v>
@@ -1603,7 +1604,7 @@
         <v>88</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>96</v>
@@ -1645,7 +1646,7 @@
         <v>88</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>103</v>
@@ -1728,7 +1729,7 @@
         <v>110</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>117</v>
@@ -1769,7 +1770,7 @@
         <v>110</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>124</v>
@@ -1851,7 +1852,7 @@
         <v>131</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>139</v>
@@ -1892,10 +1893,10 @@
         <v>131</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>146</v>
@@ -1974,7 +1975,7 @@
         <v>152</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>160</v>
@@ -2018,7 +2019,7 @@
         <v>21</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>168</v>
@@ -2030,10 +2031,10 @@
         <v>91</v>
       </c>
       <c r="I26" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>221</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>222</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
@@ -2056,10 +2057,10 @@
         <v>167</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>172</v>
@@ -2093,7 +2094,7 @@
         <v>167</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>176</v>
@@ -2134,7 +2135,7 @@
         <v>167</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>183</v>

--- a/member_list.xlsx
+++ b/member_list.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
   <si>
     <t>name</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>nastaran.divani@uni-graz.at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nastaran Divani is a linguist and researcher at the University of Graz. Her research focuses on the syntax of Kurdish, particularly on clitic systems and their role in the establishment of syntactic dependencies.  Drawing mainly on Sanandaji Kurdish, she investigates how clitics interact with verbal agreement, argument structure, and the realization of subjects and objects. Her work is situated within the generative approach to syntax, with a particular interest in what clitic systems can tell us about the structure of grammar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nastaran Divani is researcher at the University of Graz. Her research focuses on the syntax of Kurdish. Drawing mainly on Sanandaji Kurdish, she investigates how clitics interact with verbal agreement, argument structure, and the realization of subjects and objects.</t>
   </si>
   <si>
     <t xml:space="preserve">Dr. Sarah Melker</t>
@@ -1478,8 +1484,12 @@
       <c r="H5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="I5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -1492,42 +1502,42 @@
     </row>
     <row r="6" ht="38.25">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" ht="51">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
@@ -1536,22 +1546,22 @@
         <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
@@ -1566,32 +1576,32 @@
     </row>
     <row r="8" ht="51">
       <c r="A8" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
@@ -1606,34 +1616,34 @@
     </row>
     <row r="9" ht="63.75">
       <c r="A9" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
@@ -1648,28 +1658,28 @@
     </row>
     <row r="10" ht="25.5">
       <c r="A10" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1686,24 +1696,24 @@
     </row>
     <row r="11" ht="25.5">
       <c r="A11" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1720,34 +1730,34 @@
     </row>
     <row r="12" ht="76.5">
       <c r="A12" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -1762,34 +1772,34 @@
     </row>
     <row r="13" ht="63.75">
       <c r="A13" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
@@ -1804,34 +1814,34 @@
     </row>
     <row r="14" ht="63.75">
       <c r="A14" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -1846,34 +1856,34 @@
     </row>
     <row r="15" ht="51">
       <c r="A15" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -1888,34 +1898,34 @@
     </row>
     <row r="16" ht="63.75">
       <c r="A16" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
@@ -1930,34 +1940,34 @@
     </row>
     <row r="17" ht="63.75">
       <c r="A17" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
@@ -1972,34 +1982,34 @@
     </row>
     <row r="18" ht="63.75">
       <c r="A18" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
@@ -2013,34 +2023,34 @@
     </row>
     <row r="19" ht="51">
       <c r="A19" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
@@ -2054,34 +2064,34 @@
     </row>
     <row r="20" ht="38.25">
       <c r="A20" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -2095,34 +2105,34 @@
     </row>
     <row r="21" ht="76.5">
       <c r="A21" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
@@ -2136,34 +2146,34 @@
     </row>
     <row r="22" ht="51">
       <c r="A22" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
@@ -2177,34 +2187,34 @@
     </row>
     <row r="23" ht="51">
       <c r="A23" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
@@ -2218,34 +2228,34 @@
     </row>
     <row r="24" ht="63.75">
       <c r="A24" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
@@ -2259,34 +2269,34 @@
     </row>
     <row r="25" ht="69" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
@@ -2300,34 +2310,34 @@
     </row>
     <row r="26" ht="51">
       <c r="A26" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
@@ -2341,34 +2351,34 @@
     </row>
     <row r="27" ht="25.5">
       <c r="A27" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
@@ -2382,34 +2392,34 @@
     </row>
     <row r="28" ht="63.75">
       <c r="A28" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -2423,34 +2433,34 @@
     </row>
     <row r="29" ht="51">
       <c r="A29" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
@@ -30331,114 +30341,114 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -30482,18 +30492,18 @@
     </row>
     <row r="2">
       <c r="A2" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/member_list.xlsx
+++ b/member_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philippaadolf/Documents/R/Website_sfb_redefi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F6A4D7-EE7A-1D49-865A-5005B704804C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80407474-0702-8745-9952-A202E896C7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>martina.barili@uni-graz.at</t>
-  </si>
-  <si>
-    <t>Martina Barili holds a master’s degree in Language and Mind from the University of Siena. Her previous research focused on gradability and vagueness, particularly the semantics of gradable adjectives that express value judgements. Within the ReDeFi project, her current research aims to develop a novel model of grammar that incorporates the properties of redundancy and deficiency.</t>
   </si>
   <si>
     <t>Martina Barili holds a master’s degree in Language and Mind from the University of Siena. Her research interests include gradability, vagueness, and the development of grammatical models that account for redundancy and deficiency.</t>
@@ -725,6 +722,9 @@
   <si>
     <t>Melanie Loitzl, BA BA BEd MA MEd</t>
   </si>
+  <si>
+    <t>Martina Barili holds a master’s degree in Language and Mind from the University of Siena. Her thesis investigated the distribution of scale modifiers with complex adjectives to test their gradability experimentally. Her broader research interests include copular clauses, alternative semantics, and phenomena at the interface between syntax, semantics and pragmatics. Within the ReDeFi project, her current research aims to develop a novel model of grammar that incorporates the properties of redundancy and deficiency.</t>
+  </si>
 </sst>
 </file>
 
@@ -1171,11 +1171,11 @@
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="5" spans="1:28" ht="42">
       <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>12</v>
@@ -1201,20 +1201,20 @@
         <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
@@ -1228,42 +1228,42 @@
     </row>
     <row r="6" spans="1:28" ht="42">
       <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="56">
       <c r="A7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
@@ -1272,22 +1272,22 @@
         <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
@@ -1302,32 +1302,32 @@
     </row>
     <row r="8" spans="1:28" ht="42">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
@@ -1342,34 +1342,34 @@
     </row>
     <row r="9" spans="1:28" ht="70">
       <c r="A9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="C9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
@@ -1384,28 +1384,28 @@
     </row>
     <row r="10" spans="1:28" ht="28">
       <c r="A10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1422,24 +1422,24 @@
     </row>
     <row r="11" spans="1:28" ht="28">
       <c r="A11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1456,34 +1456,34 @@
     </row>
     <row r="12" spans="1:28" ht="84">
       <c r="A12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -1498,34 +1498,34 @@
     </row>
     <row r="13" spans="1:28" ht="70">
       <c r="A13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="C13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
@@ -1540,34 +1540,34 @@
     </row>
     <row r="14" spans="1:28" ht="56">
       <c r="A14" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -1582,34 +1582,34 @@
     </row>
     <row r="15" spans="1:28" ht="56">
       <c r="A15" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -1624,34 +1624,34 @@
     </row>
     <row r="16" spans="1:28" ht="70">
       <c r="A16" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" s="5" t="s">
+      <c r="J16" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
@@ -1666,34 +1666,34 @@
     </row>
     <row r="17" spans="1:28" ht="70">
       <c r="A17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I17" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
@@ -1708,34 +1708,34 @@
     </row>
     <row r="18" spans="1:28" ht="56">
       <c r="A18" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I18" s="5" t="s">
+      <c r="J18" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
@@ -1749,34 +1749,34 @@
     </row>
     <row r="19" spans="1:28" ht="56">
       <c r="A19" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
@@ -1790,34 +1790,34 @@
     </row>
     <row r="20" spans="1:28" ht="42">
       <c r="A20" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="C20" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I20" s="5" t="s">
+      <c r="J20" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -1831,34 +1831,34 @@
     </row>
     <row r="21" spans="1:28" ht="84">
       <c r="A21" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
@@ -1872,34 +1872,34 @@
     </row>
     <row r="22" spans="1:28" ht="56">
       <c r="A22" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="C22" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="H22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I22" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
@@ -1913,34 +1913,34 @@
     </row>
     <row r="23" spans="1:28" ht="56">
       <c r="A23" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
@@ -1954,34 +1954,34 @@
     </row>
     <row r="24" spans="1:28" ht="70">
       <c r="A24" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J24" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
@@ -1995,34 +1995,34 @@
     </row>
     <row r="25" spans="1:28" ht="69" customHeight="1">
       <c r="A25" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I25" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
@@ -2036,34 +2036,34 @@
     </row>
     <row r="26" spans="1:28" ht="56">
       <c r="A26" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="5" t="s">
+      <c r="J26" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
@@ -2077,34 +2077,34 @@
     </row>
     <row r="27" spans="1:28" ht="56">
       <c r="A27" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I27" s="5" t="s">
+      <c r="J27" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>188</v>
       </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
@@ -2118,34 +2118,34 @@
     </row>
     <row r="28" spans="1:28" ht="70">
       <c r="A28" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I28" s="5" t="s">
+      <c r="J28" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -2159,34 +2159,34 @@
     </row>
     <row r="29" spans="1:28" ht="42">
       <c r="A29" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="C29" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="I29" s="5" t="s">
+      <c r="J29" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
@@ -30066,114 +30066,114 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>225</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>226</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>228</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -30216,18 +30216,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/member_list.xlsx
+++ b/member_list.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t>name</t>
   </si>
@@ -98,6 +98,9 @@
     <t>/img/pictures/Martina_Barili.jpeg</t>
   </si>
   <si>
+    <t>https://online.uni-graz.at/kfu_online/visitenkarte.show_vcard?pPersonenId=4342CAA181B5B999&amp;pPersonenGruppe=3</t>
+  </si>
+  <si>
     <t>martina.barili@uni-graz.at</t>
   </si>
   <si>
@@ -114,6 +117,9 @@
   </si>
   <si>
     <t>/img/pictures/Nastaran_Divani.jpg</t>
+  </si>
+  <si>
+    <t>https://online.uni-graz.at/kfu_online/visitenkarte.show_vcard?pPersonenId=5665CCF31AC39477&amp;pPersonenGruppe=3</t>
   </si>
   <si>
     <t>nastaran.divani@uni-graz.at</t>
@@ -180,6 +186,9 @@
   </si>
   <si>
     <t>/img/pictures/Susi_Wurmbrand.jpg</t>
+  </si>
+  <si>
+    <t>https://www.plus.ac.at/linguistik/der-fachbereich/mitarbeiterinnen/univ-prof-susanne-wurmbrand-phd/</t>
   </si>
   <si>
     <t>susanne.wurmbrand@plus.ac.at</t>
@@ -458,7 +467,7 @@
     <t>/img/pictures/Andrea_Miglietta.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">https://ucrisportal.univie.ac.at/en/persons/andrea-miglietta (https://homepage.univie.ac.at/andrea.miglietta/)</t>
+    <t>https://homepage.univie.ac.at/andrea.miglietta/</t>
   </si>
   <si>
     <t>andrea.miglietta@univie.ac.at</t>
@@ -1428,18 +1437,20 @@
       <c r="E4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="G4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
@@ -1453,10 +1464,10 @@
     </row>
     <row r="5" ht="51">
       <c r="A5" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>12</v>
@@ -1465,20 +1476,22 @@
         <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="G5" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
@@ -1492,42 +1505,42 @@
     </row>
     <row r="6" ht="38.25">
       <c r="A6" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" ht="51">
       <c r="A7" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
@@ -1536,22 +1549,22 @@
         <v>24</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
@@ -1566,32 +1579,34 @@
     </row>
     <row r="8" ht="51">
       <c r="A8" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="5"/>
+        <v>55</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="G8" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
@@ -1606,34 +1621,34 @@
     </row>
     <row r="9" ht="63.75">
       <c r="A9" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
@@ -1648,28 +1663,28 @@
     </row>
     <row r="10" ht="25.5">
       <c r="A10" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1686,34 +1701,34 @@
     </row>
     <row r="11" ht="76.5">
       <c r="A11" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
@@ -1728,34 +1743,34 @@
     </row>
     <row r="12" ht="63.75">
       <c r="A12" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -1770,34 +1785,34 @@
     </row>
     <row r="13" ht="63.75">
       <c r="A13" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
@@ -1812,34 +1827,34 @@
     </row>
     <row r="14" ht="51">
       <c r="A14" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -1854,34 +1869,34 @@
     </row>
     <row r="15" ht="63.75">
       <c r="A15" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -1896,34 +1911,34 @@
     </row>
     <row r="16" ht="63.75">
       <c r="A16" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
@@ -1938,34 +1953,34 @@
     </row>
     <row r="17" ht="63.75">
       <c r="A17" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
@@ -1979,34 +1994,34 @@
     </row>
     <row r="18" ht="51">
       <c r="A18" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6"/>
@@ -2020,34 +2035,34 @@
     </row>
     <row r="19" ht="38.25">
       <c r="A19" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
@@ -2061,34 +2076,34 @@
     </row>
     <row r="20" ht="76.5">
       <c r="A20" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -2102,34 +2117,34 @@
     </row>
     <row r="21" ht="51">
       <c r="A21" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
@@ -2143,34 +2158,34 @@
     </row>
     <row r="22" ht="51">
       <c r="A22" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6"/>
@@ -2184,34 +2199,34 @@
     </row>
     <row r="23" ht="63.75">
       <c r="A23" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
@@ -2225,34 +2240,34 @@
     </row>
     <row r="24" ht="69" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
@@ -2266,34 +2281,34 @@
     </row>
     <row r="25" ht="51">
       <c r="A25" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
@@ -2307,34 +2322,34 @@
     </row>
     <row r="26" ht="51">
       <c r="A26" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
@@ -2348,34 +2363,34 @@
     </row>
     <row r="27" ht="63.75">
       <c r="A27" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
@@ -2389,34 +2404,34 @@
     </row>
     <row r="28" ht="51">
       <c r="A28" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -30272,6 +30287,12 @@
       <c r="AB959" s="6"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="F4"/>
+    <hyperlink r:id="rId2" ref="F5"/>
+    <hyperlink r:id="rId3" ref="F8"/>
+    <hyperlink r:id="rId4" ref="F21"/>
+  </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.51181102362204689" footer="0.51181102362204689"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -30297,119 +30318,119 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" ht="13">
       <c r="A16" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -30453,18 +30474,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/member_list.xlsx
+++ b/member_list.xlsx
@@ -170,10 +170,10 @@
     <t>simon.dampfhofer@uni-graz.at</t>
   </si>
   <si>
-    <t xml:space="preserve">Simon Dampfhofer holds an MA in German Linguistics and Philology, for which he wrote a thesis on the semantics of German indefinites, as well as a BSc in Physics. He has also pursued further academic studies in physics and philosophy. His background includes formal semantics, empirical research, and statistical methodology, and he has contributed to the implementation of several experiments at the Institute for German Studies at the University of Graz. He has participated in workshops, conferences, and summer schools, including ÖLT, ICSH, and the DGfS Summer School. His research interests include the syntax and semantics of pronouns, theories of gender, and the philosophy of language.</t>
+    <t xml:space="preserve">Besides a M.A. in German linguistics and philology (with a thesis on the semantics of German indefinites), Simon Dampfhofer holds a B.Sc. in Physics and is currently engaged in further academic studies in the areas of Physics and Philosophy. He has prior experience in formal semantics, empirical and statistical methodology, as well as implementation of empirical linguistic experiments. Current research interests include syntax and semantics of pronouns as well as of phi features, discourse representation, and philosophy of language.</t>
   </si>
   <si>
-    <t xml:space="preserve">Simon Dampfhofer holds an MA in German Linguistics and Philology and a BSc in Physics, with additional academic training in philosophy. His research interests include formal semantics, the syntax and semantics of pronouns, theories of gender, and the philosophy of language.</t>
+    <t xml:space="preserve">Simon Dampfhofer holds an MA in German Linguistics and Philology and a BSc in Physics, with additional academic training in philosophy. His research interests include formal semantics, the  syntax and semantics of pronouns as well as of phi features, discourse representation, and philosophy of language.</t>
   </si>
   <si>
     <t xml:space="preserve">Univ.-Prof. Mag., PhD. Susanne Wurmbrand</t>
@@ -1428,7 +1428,7 @@
       <c r="AB3" s="6"/>
     </row>
     <row r="4" ht="38.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1566,10 +1566,10 @@
       <c r="H7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="7" t="s">
         <v>51</v>
       </c>
       <c r="S7" s="6"/>
@@ -1583,8 +1583,8 @@
       <c r="AA7" s="6"/>
       <c r="AB7" s="6"/>
     </row>
-    <row r="8" ht="51">
-      <c r="A8" s="7" t="s">
+    <row r="8" ht="38.25">
+      <c r="A8" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -1608,10 +1608,10 @@
       <c r="H8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="5" t="s">
         <v>60</v>
       </c>
       <c r="S8" s="6"/>
@@ -1626,7 +1626,7 @@
       <c r="AB8" s="6"/>
     </row>
     <row r="9" ht="63.75">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1748,7 +1748,7 @@
       <c r="AB11" s="6"/>
     </row>
     <row r="12" ht="63.75">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -1790,7 +1790,7 @@
       <c r="AB12" s="6"/>
     </row>
     <row r="13" ht="63.75">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1832,7 +1832,7 @@
       <c r="AB13" s="6"/>
     </row>
     <row r="14" ht="51">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1958,7 +1958,7 @@
       <c r="AB16" s="6"/>
     </row>
     <row r="17" ht="63.75">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>118</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1999,7 +1999,7 @@
       <c r="AB17" s="6"/>
     </row>
     <row r="18" ht="51">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -2162,7 +2162,7 @@
       <c r="AA21" s="6"/>
       <c r="AB21" s="6"/>
     </row>
-    <row r="22" ht="51">
+    <row r="22" ht="63.75">
       <c r="A22" s="5" t="s">
         <v>155</v>
       </c>
@@ -2187,10 +2187,10 @@
       <c r="H22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="5" t="s">
         <v>161</v>
       </c>
       <c r="T22" s="6"/>
@@ -2204,7 +2204,7 @@
       <c r="AB22" s="6"/>
     </row>
     <row r="23" ht="63.75">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -2245,7 +2245,7 @@
       <c r="AB23" s="6"/>
     </row>
     <row r="24" ht="69" customHeight="1">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>170</v>
       </c>
       <c r="B24" s="5" t="s">
